--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Clinical Dictionary/GDC_Clinical_DM.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Clinical Dictionary/GDC_Clinical_DM.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Clinical Dictionary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C45B67-3DF3-A24C-9F44-C1B500D1BB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DE0C15-CB55-4448-A1C2-1423A51EB18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="8000" windowWidth="27240" windowHeight="16440"/>
+    <workbookView xWindow="900" yWindow="1520" windowWidth="22420" windowHeight="16300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GDC_Clinical_DM" sheetId="1" r:id="rId1"/>
+    <sheet name="InfoSheet" sheetId="2" r:id="rId1"/>
+    <sheet name="Prefixes" sheetId="3" r:id="rId2"/>
+    <sheet name="Mapping Process" sheetId="4" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="5" r:id="rId4"/>
+    <sheet name="New Concepts" sheetId="6" r:id="rId5"/>
+    <sheet name="Codebook" sheetId="7" r:id="rId6"/>
+    <sheet name="Dictionary Mapping" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="118">
   <si>
     <t>Column</t>
   </si>
@@ -79,39 +85,21 @@
     <t>TARGET USI</t>
   </si>
   <si>
-    <t>sio:Identifier</t>
-  </si>
-  <si>
     <t>??subject</t>
   </si>
   <si>
     <t>Gender</t>
   </si>
   <si>
-    <t>sio:BiologicalSex</t>
-  </si>
-  <si>
     <t>Race</t>
   </si>
   <si>
-    <t>sio:Race</t>
-  </si>
-  <si>
     <t>Ethnicity</t>
   </si>
   <si>
-    <t>sio:Ethnicity</t>
-  </si>
-  <si>
     <t>Age at Diagnosis in Days</t>
   </si>
   <si>
-    <t>sio:Age</t>
-  </si>
-  <si>
-    <t>sio:Day</t>
-  </si>
-  <si>
     <t>??diagnosis</t>
   </si>
   <si>
@@ -127,18 +115,12 @@
     <t>Time to First Event in Days</t>
   </si>
   <si>
-    <t>sio:TimeInterval</t>
-  </si>
-  <si>
     <t>??first_event</t>
   </si>
   <si>
     <t xml:space="preserve">Vital Status </t>
   </si>
   <si>
-    <t>sio:LifeStatus</t>
-  </si>
-  <si>
     <t>Overall Survival Time in Days</t>
   </si>
   <si>
@@ -151,15 +133,6 @@
     <t>Year of Diagnosis</t>
   </si>
   <si>
-    <t>sio:TimeInstant</t>
-  </si>
-  <si>
-    <t>YYYY^^xsd:gYear</t>
-  </si>
-  <si>
-    <t>sio:Year</t>
-  </si>
-  <si>
     <t>Year of Last Follow Up</t>
   </si>
   <si>
@@ -169,21 +142,12 @@
     <t>Protocol</t>
   </si>
   <si>
-    <t>sio:ExperimentalProtocol</t>
-  </si>
-  <si>
     <t>Disease at diagnosis</t>
   </si>
   <si>
-    <t>sio:Disease</t>
-  </si>
-  <si>
     <t>Metastasis site</t>
   </si>
   <si>
-    <t>sio:Site</t>
-  </si>
-  <si>
     <t>??metastasis</t>
   </si>
   <si>
@@ -208,9 +172,6 @@
     <t>Specific tumor region</t>
   </si>
   <si>
-    <t>sio:SpatialRegion</t>
-  </si>
-  <si>
     <t>Definitive Surgery</t>
   </si>
   <si>
@@ -280,21 +241,9 @@
     <t>ncit:C49236</t>
   </si>
   <si>
-    <t>sio:Comment</t>
-  </si>
-  <si>
-    <t>sio:Human</t>
-  </si>
-  <si>
-    <t>sio:SubjectRole</t>
-  </si>
-  <si>
     <t>??study</t>
   </si>
   <si>
-    <t>sio:Diagnosis</t>
-  </si>
-  <si>
     <t>??last</t>
   </si>
   <si>
@@ -307,9 +256,6 @@
     <t>hp:0002664, ncit:C3262</t>
   </si>
   <si>
-    <t>sio:isPartOf</t>
-  </si>
-  <si>
     <t>ncit:C8509</t>
   </si>
   <si>
@@ -332,13 +278,115 @@
   </si>
   <si>
     <t>ncit:C25551</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>hasco</t>
+  </si>
+  <si>
+    <t>http://hadatac.org/ont/hasco/</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/HP_</t>
+  </si>
+  <si>
+    <t>ncit</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/resource/</t>
+  </si>
+  <si>
+    <t>uo</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/UO_</t>
+  </si>
+  <si>
+    <t>oae</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/OAE_</t>
+  </si>
+  <si>
+    <t>sio:SIO_000115</t>
+  </si>
+  <si>
+    <t>sio:SIO_010029</t>
+  </si>
+  <si>
+    <t>sio:SIO_001015</t>
+  </si>
+  <si>
+    <t>sio:SIO_001014</t>
+  </si>
+  <si>
+    <t>sio:SIO_001013</t>
+  </si>
+  <si>
+    <t>YYYY</t>
+  </si>
+  <si>
+    <t>sio:SIO_000417</t>
+  </si>
+  <si>
+    <t>sio:SIO_010057</t>
+  </si>
+  <si>
+    <t>sio:SIO_000418</t>
+  </si>
+  <si>
+    <t>sio:SIO_001043</t>
+  </si>
+  <si>
+    <t>sio:SIO_010299</t>
+  </si>
+  <si>
+    <t>sio:SIO_000019</t>
+  </si>
+  <si>
+    <t>sio:SIO_000370</t>
+  </si>
+  <si>
+    <t>sio:SIO_001167</t>
+  </si>
+  <si>
+    <t>sio:SIO_000430</t>
+  </si>
+  <si>
+    <t>sio:SIO_000428</t>
+  </si>
+  <si>
+    <t>sio:SIO_000485</t>
+  </si>
+  <si>
+    <t>sio:SIO_000883</t>
+  </si>
+  <si>
+    <t>sio:SIO_001331</t>
+  </si>
+  <si>
+    <t>sio:SIO_000068</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -473,8 +521,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -654,8 +722,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -770,8 +844,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -814,11 +903,20 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="42" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -852,6 +950,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1171,9 +1270,207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8431D928-A5F3-5247-AA0E-D172FCC24585}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE44E62C-5FBC-2242-854B-C89875F37DEB}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{46D90A0F-88C0-D24E-8238-B33EF20572E3}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{DBAB73B5-2210-AB4A-ADF0-6D37FF7EAA16}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{97D681D1-3EF8-574B-97FA-C20115C75041}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{514DA736-3065-FD41-96E7-6952D453B676}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{517B8618-FC75-084B-890B-0C96A03ED11C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8CF68B-9D17-8843-8291-81ECD282FF3B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06299E36-C6E1-C944-A84A-4999B266FDF6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD019FB2-D41C-BC45-822B-03A87C165167}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F3E6AF-EBF7-FE4B-9C32-E7317218F680}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1236,10 +1533,10 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
         <v>18</v>
@@ -1247,433 +1544,433 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
         <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="N11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="N12" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N17" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N19" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="R20" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="N21" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" t="s">
         <v>53</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="N22" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="N23" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="N24" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="N25" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="N26" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N27" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="N28" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N29" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
@@ -1681,10 +1978,10 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N31" t="s">
         <v>16</v>
@@ -1692,188 +1989,189 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="J32" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G44" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R46" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>